--- a/excel/XOR_perceptron_optimization_backprpagation_sgd.xlsx
+++ b/excel/XOR_perceptron_optimization_backprpagation_sgd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13615A50-080B-4614-8284-6F13291E45AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4507E2-E3DB-494B-872E-A559540C703F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="186" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -294,116 +294,116 @@
   </cellStyleXfs>
   <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -476,8 +476,8 @@
       <xdr:rowOff>6787</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>777240</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>320040</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>15631</xdr:rowOff>
     </xdr:to>
@@ -779,17 +779,21 @@
   <dimension ref="A1:AB991"/>
   <sheetFormatPr defaultColWidth="9.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="9.44140625" style="3"/>
+    <col min="1" max="4" width="9.44140625" style="3"/>
+    <col min="5" max="5" width="2.21875" style="3" customWidth="1"/>
+    <col min="6" max="8" width="9.44140625" style="3"/>
     <col min="9" max="9" width="14.33203125" style="3" customWidth="1"/>
     <col min="10" max="10" width="13.88671875" style="3" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" style="3" customWidth="1"/>
-    <col min="12" max="16" width="9.44140625" style="3"/>
+    <col min="12" max="12" width="9.44140625" style="3"/>
+    <col min="13" max="13" width="3.33203125" style="3" customWidth="1"/>
+    <col min="14" max="16" width="9.44140625" style="3"/>
     <col min="17" max="17" width="10.109375" style="3" customWidth="1"/>
     <col min="18" max="18" width="32.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="9.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="38" customFormat="1" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28" s="38" customFormat="1" ht="55.8" x14ac:dyDescent="0.45">
       <c r="A1" s="33"/>
       <c r="B1" s="34" t="s">
         <v>0</v>
@@ -865,19 +869,19 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5">
         <f t="shared" ref="F2:H2" ca="1" si="0">RAND()</f>
-        <v>0.98370082358421951</v>
+        <v>0.66915033172270433</v>
       </c>
       <c r="G2" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>0.78460329974436338</v>
+        <v>0.38786560725316099</v>
       </c>
       <c r="H2" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>0.14471475521494259</v>
+        <v>0.80583811429452423</v>
       </c>
       <c r="I2" s="6">
         <f t="shared" ref="I2:I17" ca="1" si="1">B2*F2+C2*G2+D2*H2</f>
-        <v>0.98370082358421951</v>
+        <v>0.66915033172270433</v>
       </c>
       <c r="J2" s="6">
         <f t="shared" ref="J2:J17" ca="1" si="2">IF(I2&gt;=0, 1, 0)</f>
@@ -934,19 +938,19 @@
       <c r="E3" s="12"/>
       <c r="F3" s="5">
         <f t="shared" ref="F3:H3" ca="1" si="4">RAND()</f>
-        <v>0.75775524455845378</v>
+        <v>0.65010413781974474</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>3.7666495940032463E-2</v>
+        <v>4.6212108755248837E-2</v>
       </c>
       <c r="H3" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>0.6012387431231897</v>
+        <v>0.30118874472268076</v>
       </c>
       <c r="I3" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1.3589939876816435</v>
+        <v>0.9512928825424255</v>
       </c>
       <c r="J3" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -1001,19 +1005,19 @@
       <c r="E4" s="12"/>
       <c r="F4" s="5">
         <f t="shared" ref="F4:H4" ca="1" si="6">RAND()</f>
-        <v>5.3743629383369407E-2</v>
+        <v>0.67392270302016688</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39946798460384358</v>
+        <v>0.73198030855023577</v>
       </c>
       <c r="H4" s="5">
         <f t="shared" ca="1" si="6"/>
-        <v>0.93249576813251644</v>
+        <v>0.10793890425945685</v>
       </c>
       <c r="I4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0.45321161398721299</v>
+        <v>1.4059030115704028</v>
       </c>
       <c r="J4" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -1068,19 +1072,19 @@
       <c r="E5" s="17"/>
       <c r="F5" s="5">
         <f t="shared" ref="F5:H5" ca="1" si="8">RAND()</f>
-        <v>5.497281481467442E-2</v>
+        <v>0.85698842388823737</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>0.48575147193579282</v>
+        <v>5.8565288539551341E-2</v>
       </c>
       <c r="H5" s="5">
         <f t="shared" ca="1" si="8"/>
-        <v>0.62641207494297835</v>
+        <v>0.65275776303257793</v>
       </c>
       <c r="I5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>1.1671363616934456</v>
+        <v>1.5683114754603666</v>
       </c>
       <c r="J5" s="2">
         <f t="shared" ca="1" si="2"/>
@@ -1138,7 +1142,7 @@
         <v>-0.5</v>
       </c>
       <c r="G6" s="21">
-        <f t="shared" ref="F6:H6" ca="1" si="10">O2</f>
+        <f t="shared" ref="G6:H6" ca="1" si="10">O2</f>
         <v>0</v>
       </c>
       <c r="H6" s="21">

--- a/excel/XOR_perceptron_optimization_backprpagation_sgd.xlsx
+++ b/excel/XOR_perceptron_optimization_backprpagation_sgd.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\statistics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\조근하\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4507E2-E3DB-494B-872E-A559540C703F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8413D5A4-2ABD-4A01-829C-35BD2AD39A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,9 +42,6 @@
     <t>w2</t>
   </si>
   <si>
-    <t>sum_product</t>
-  </si>
-  <si>
     <t>Y(output)
 Activation Function</t>
   </si>
@@ -70,6 +67,11 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=t3VBY9OisCo&amp;t=11s</t>
+  </si>
+  <si>
+    <t>sum_product
+inner product</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -292,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -352,9 +354,6 @@
     <xf numFmtId="176" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -405,6 +404,15 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,7 +485,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>320040</xdr:colOff>
+      <xdr:colOff>45720</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>15631</xdr:rowOff>
     </xdr:to>
@@ -782,7 +790,7 @@
     <col min="1" max="4" width="9.44140625" style="3"/>
     <col min="5" max="5" width="2.21875" style="3" customWidth="1"/>
     <col min="6" max="8" width="9.44140625" style="3"/>
-    <col min="9" max="9" width="14.33203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" style="3" customWidth="1"/>
     <col min="10" max="10" width="13.88671875" style="3" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.44140625" style="3"/>
@@ -793,65 +801,65 @@
     <col min="19" max="16384" width="9.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="38" customFormat="1" ht="55.8" x14ac:dyDescent="0.45">
-      <c r="A1" s="33"/>
-      <c r="B1" s="34" t="s">
+    <row r="1" spans="1:28" s="37" customFormat="1" ht="55.8" x14ac:dyDescent="0.45">
+      <c r="A1" s="32"/>
+      <c r="B1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34" t="s">
+      <c r="E1" s="33"/>
+      <c r="F1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="K1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="L1" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="35" t="s">
+      <c r="M1" s="33"/>
+      <c r="N1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34" t="s">
+      <c r="O1" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="34" t="s">
+      <c r="P1" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="34" t="s">
+      <c r="Q1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="36" t="s">
+      <c r="R1" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
     </row>
     <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="4">
@@ -867,31 +875,31 @@
         <v>0</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="5">
+      <c r="F2" s="40">
         <f t="shared" ref="F2:H2" ca="1" si="0">RAND()</f>
-        <v>0.66915033172270433</v>
+        <v>0.16158631980313487</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>0.38786560725316099</v>
+        <v>0.19953608466488137</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="40">
         <f t="shared" ca="1" si="0"/>
-        <v>0.80583811429452423</v>
+        <v>4.7910712286809432E-2</v>
       </c>
       <c r="I2" s="6">
-        <f t="shared" ref="I2:I17" ca="1" si="1">B2*F2+C2*G2+D2*H2</f>
-        <v>0.66915033172270433</v>
+        <f ca="1">SUMPRODUCT(B2:D2,F2:H2)</f>
+        <v>0.16158631980313487</v>
       </c>
       <c r="J2" s="6">
-        <f t="shared" ref="J2:J17" ca="1" si="2">IF(I2&gt;=0, 1, 0)</f>
+        <f t="shared" ref="J2:J17" ca="1" si="1">IF(I2&gt;=0, 1, 0)</f>
         <v>1</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
       </c>
       <c r="L2" s="7">
-        <f t="shared" ref="L2:L17" ca="1" si="3">K2-J2</f>
+        <f t="shared" ref="L2:L17" ca="1" si="2">K2-J2</f>
         <v>-1</v>
       </c>
       <c r="M2" s="6"/>
@@ -936,31 +944,31 @@
         <v>1</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="5">
-        <f t="shared" ref="F3:H3" ca="1" si="4">RAND()</f>
-        <v>0.65010413781974474</v>
+      <c r="F3" s="40">
+        <f t="shared" ref="F3:H3" ca="1" si="3">RAND()</f>
+        <v>0.78180705851977583</v>
       </c>
-      <c r="G3" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>4.6212108755248837E-2</v>
+      <c r="G3" s="40">
+        <f t="shared" ca="1" si="3"/>
+        <v>7.7068297758697391E-2</v>
       </c>
-      <c r="H3" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.30118874472268076</v>
+      <c r="H3" s="40">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.32102882210995964</v>
       </c>
       <c r="I3" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.9512928825424255</v>
+        <f t="shared" ref="I3:I17" ca="1" si="4">SUMPRODUCT(B3:D3,F3:H3)</f>
+        <v>1.1028358806297356</v>
       </c>
       <c r="J3" s="1">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="K3" s="12">
         <v>1</v>
       </c>
       <c r="L3" s="13">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="M3" s="1"/>
@@ -1003,31 +1011,31 @@
         <v>0</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="5">
+      <c r="F4" s="40">
         <f t="shared" ref="F4:H4" ca="1" si="6">RAND()</f>
-        <v>0.67392270302016688</v>
+        <v>0.94537968504943248</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="40">
         <f t="shared" ca="1" si="6"/>
-        <v>0.73198030855023577</v>
+        <v>0.90017377033857948</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="40">
         <f t="shared" ca="1" si="6"/>
-        <v>0.10793890425945685</v>
+        <v>0.37687210242799762</v>
       </c>
       <c r="I4" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.4059030115704028</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1.845553455388012</v>
       </c>
       <c r="J4" s="1">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="K4" s="12">
         <v>1</v>
       </c>
       <c r="L4" s="13">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="M4" s="1"/>
@@ -1070,31 +1078,31 @@
         <v>1</v>
       </c>
       <c r="E5" s="17"/>
-      <c r="F5" s="5">
+      <c r="F5" s="40">
         <f t="shared" ref="F5:H5" ca="1" si="8">RAND()</f>
-        <v>0.85698842388823737</v>
+        <v>0.31926236834098509</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="40">
         <f t="shared" ca="1" si="8"/>
-        <v>5.8565288539551341E-2</v>
+        <v>0.44869619363943802</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="40">
         <f t="shared" ca="1" si="8"/>
-        <v>0.65275776303257793</v>
+        <v>0.98091764888279331</v>
       </c>
       <c r="I5" s="2">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.5683114754603666</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1.7488762108632163</v>
       </c>
       <c r="J5" s="2">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="K5" s="17">
         <v>0</v>
       </c>
       <c r="L5" s="18">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v>-1</v>
       </c>
       <c r="M5" s="2"/>
@@ -1137,31 +1145,31 @@
         <v>0</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="21">
+      <c r="F6" s="39">
         <f ca="1">N2</f>
         <v>-0.5</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="39">
         <f t="shared" ref="G6:H6" ca="1" si="10">O2</f>
         <v>0</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="39">
         <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
-      <c r="I6" s="22">
-        <f t="shared" ca="1" si="1"/>
+      <c r="I6" s="21">
+        <f t="shared" ca="1" si="4"/>
         <v>-0.5</v>
       </c>
       <c r="J6" s="6">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="K6" s="6">
         <v>0</v>
       </c>
       <c r="L6" s="7">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="M6" s="6"/>
@@ -1173,7 +1181,7 @@
         <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
-      <c r="P6" s="23">
+      <c r="P6" s="22">
         <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
@@ -1204,31 +1212,31 @@
         <v>1</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="24">
+      <c r="F7" s="23">
         <f t="shared" ref="F7:H7" ca="1" si="12">N3</f>
         <v>0</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="23">
         <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="23">
         <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
-      <c r="I7" s="25">
-        <f t="shared" ca="1" si="1"/>
+      <c r="I7" s="24">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="13">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="M7" s="1"/>
@@ -1240,7 +1248,7 @@
         <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
-      <c r="P7" s="26">
+      <c r="P7" s="25">
         <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
@@ -1271,31 +1279,31 @@
         <v>0</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="24">
+      <c r="F8" s="23">
         <f t="shared" ref="F8:H8" ca="1" si="14">N4</f>
         <v>0</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="23">
         <f t="shared" ca="1" si="14"/>
         <v>0</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="23">
         <f t="shared" ca="1" si="14"/>
         <v>0</v>
       </c>
-      <c r="I8" s="25">
-        <f t="shared" ca="1" si="1"/>
+      <c r="I8" s="24">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="13">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="M8" s="1"/>
@@ -1307,7 +1315,7 @@
         <f t="shared" ca="1" si="15"/>
         <v>0</v>
       </c>
-      <c r="P8" s="26">
+      <c r="P8" s="25">
         <f t="shared" ca="1" si="15"/>
         <v>0</v>
       </c>
@@ -1337,31 +1345,31 @@
         <v>1</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="27">
+      <c r="F9" s="26">
         <f t="shared" ref="F9:H9" ca="1" si="16">N5</f>
         <v>-0.5</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="26">
         <f t="shared" ca="1" si="16"/>
         <v>-0.5</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="26">
         <f t="shared" ca="1" si="16"/>
         <v>-0.5</v>
       </c>
-      <c r="I9" s="28">
-        <f t="shared" ca="1" si="1"/>
+      <c r="I9" s="27">
+        <f t="shared" ca="1" si="4"/>
         <v>-1.5</v>
       </c>
       <c r="J9" s="2">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="K9" s="2">
         <v>0</v>
       </c>
       <c r="L9" s="18">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="M9" s="2"/>
@@ -1373,7 +1381,7 @@
         <f t="shared" ca="1" si="17"/>
         <v>0</v>
       </c>
-      <c r="P9" s="29">
+      <c r="P9" s="28">
         <f t="shared" ca="1" si="17"/>
         <v>0</v>
       </c>
@@ -1417,18 +1425,18 @@
         <v>0</v>
       </c>
       <c r="I10" s="6">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="J10" s="6">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="K10" s="6">
         <v>0</v>
       </c>
       <c r="L10" s="7">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v>-1</v>
       </c>
       <c r="M10" s="6"/>
@@ -1440,7 +1448,7 @@
         <f t="shared" ca="1" si="19"/>
         <v>0</v>
       </c>
-      <c r="P10" s="23">
+      <c r="P10" s="22">
         <f t="shared" ca="1" si="19"/>
         <v>0</v>
       </c>
@@ -1484,18 +1492,18 @@
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="13">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="M11" s="1"/>
@@ -1507,7 +1515,7 @@
         <f t="shared" ca="1" si="21"/>
         <v>0</v>
       </c>
-      <c r="P11" s="26">
+      <c r="P11" s="25">
         <f t="shared" ca="1" si="21"/>
         <v>0</v>
       </c>
@@ -1551,18 +1559,18 @@
         <v>0</v>
       </c>
       <c r="I12" s="1">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="13">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="M12" s="1"/>
@@ -1574,7 +1582,7 @@
         <f t="shared" ca="1" si="23"/>
         <v>0</v>
       </c>
-      <c r="P12" s="26">
+      <c r="P12" s="25">
         <f t="shared" ca="1" si="23"/>
         <v>0</v>
       </c>
@@ -1618,18 +1626,18 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>
       </c>
       <c r="L13" s="18">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v>-1</v>
       </c>
       <c r="M13" s="2"/>
@@ -1641,7 +1649,7 @@
         <f t="shared" ca="1" si="25"/>
         <v>-0.5</v>
       </c>
-      <c r="P13" s="29">
+      <c r="P13" s="28">
         <f t="shared" ca="1" si="25"/>
         <v>-0.5</v>
       </c>
@@ -1685,18 +1693,18 @@
         <v>0</v>
       </c>
       <c r="I14" s="1">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-0.5</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
       </c>
-      <c r="L14" s="30">
-        <f t="shared" ca="1" si="3"/>
+      <c r="L14" s="29">
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="M14" s="1"/>
@@ -1752,18 +1760,18 @@
         <v>0</v>
       </c>
       <c r="I15" s="1">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
-      <c r="L15" s="31">
-        <f t="shared" ca="1" si="3"/>
+      <c r="L15" s="30">
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="M15" s="1"/>
@@ -1819,18 +1827,18 @@
         <v>0</v>
       </c>
       <c r="I16" s="1">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
-      <c r="L16" s="31">
-        <f t="shared" ca="1" si="3"/>
+      <c r="L16" s="30">
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="M16" s="1"/>
@@ -1886,18 +1894,18 @@
         <v>-0.5</v>
       </c>
       <c r="I17" s="1">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="4"/>
         <v>-1.5</v>
       </c>
       <c r="J17" s="1">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
       </c>
-      <c r="L17" s="32">
-        <f t="shared" ca="1" si="3"/>
+      <c r="L17" s="31">
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="M17" s="1"/>
